--- a/Assets/GameResource/Excel/初始卡牌配置.xlsx
+++ b/Assets/GameResource/Excel/初始卡牌配置.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385F207B-DBBF-42DA-A220-56D1C68B0962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAED70B-4281-4CE3-A368-3A6021AC437A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,18 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>起剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>走剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>步月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AutoId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,6 +68,10 @@
   </si>
   <si>
     <t>CardName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑来</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,13 +409,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -533,7 +525,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -544,7 +536,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -555,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
